--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.6995332448906</v>
+        <v>7.101174152294722</v>
       </c>
       <c r="D2" t="n">
-        <v>4.031128874149275</v>
+        <v>0.6550584420492571</v>
       </c>
       <c r="E2" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F2" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.91037445024352</v>
+        <v>10.71043584816457</v>
       </c>
       <c r="D3" t="n">
-        <v>9.856092632654736</v>
+        <v>1.601615052806395</v>
       </c>
       <c r="E3" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F3" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.04592885186855</v>
+        <v>4.232463438428639</v>
       </c>
       <c r="D4" t="n">
-        <v>19.60229578391266</v>
+        <v>3.185373064885807</v>
       </c>
       <c r="E4" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F4" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.81625641743148</v>
+        <v>7.932641667832616</v>
       </c>
       <c r="D5" t="n">
-        <v>30.22002647252315</v>
+        <v>4.910754301785012</v>
       </c>
       <c r="E5" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F5" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.85006281314158</v>
+        <v>2.413135207135507</v>
       </c>
       <c r="D6" t="n">
-        <v>11.68279372135801</v>
+        <v>1.898453979720677</v>
       </c>
       <c r="E6" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F6" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.56980789334015</v>
+        <v>8.867593782667774</v>
       </c>
       <c r="D7" t="n">
-        <v>21.2737495393003</v>
+        <v>3.4569843001363</v>
       </c>
       <c r="E7" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F7" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.00020668514009</v>
+        <v>7.800033586335264</v>
       </c>
       <c r="D8" t="n">
-        <v>31.81980515339464</v>
+        <v>5.170718337426629</v>
       </c>
       <c r="E8" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F8" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.65218414172703</v>
+        <v>5.955979923030642</v>
       </c>
       <c r="D9" t="n">
-        <v>37.02221075222346</v>
+        <v>6.016109247236312</v>
       </c>
       <c r="E9" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F9" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.8138798339967</v>
+        <v>2.082255473024464</v>
       </c>
       <c r="D10" t="n">
-        <v>12.93731994102846</v>
+        <v>2.102314490417124</v>
       </c>
       <c r="E10" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F10" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.35834314685294</v>
+        <v>4.770730761363604</v>
       </c>
       <c r="D11" t="n">
-        <v>28.93527259246057</v>
+        <v>4.701981796274843</v>
       </c>
       <c r="E11" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F11" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.86350670407708</v>
+        <v>2.902819839412525</v>
       </c>
       <c r="D12" t="n">
-        <v>17.85246505905207</v>
+        <v>2.901025572095961</v>
       </c>
       <c r="E12" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F12" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.21020383713187</v>
+        <v>8.484158123533929</v>
       </c>
       <c r="D13" t="n">
-        <v>51.41254710671316</v>
+        <v>8.35453890484089</v>
       </c>
       <c r="E13" t="n">
-        <v>16.57766858122227</v>
+        <v>2.693871144448619</v>
       </c>
       <c r="F13" t="n">
-        <v>12.81907497871222</v>
+        <v>2.083099684040735</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
